--- a/esyluban/examples/dev/DataTables/test/test_index.xlsx
+++ b/esyluban/examples/dev/DataTables/test/test_index.xlsx
@@ -1018,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="4"/>
   <sheetData>
     <row r="1">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t>full_name="test.TbTestIndex" &amp; value_type="test.TestIndex" &amp; read_schema_from_file="false" &amp; input="test/test_index.xlsx" &amp; output="test_tbtestindex"</t>
+          <t>full_name="test.TbTestIndex" &amp; input="test/test_index.xlsx"</t>
         </is>
       </c>
     </row>
@@ -1137,19 +1137,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C1:G1"/>

--- a/esyluban/examples/dev/DataTables/test/test_index.xlsx
+++ b/esyluban/examples/dev/DataTables/test/test_index.xlsx
@@ -1139,7 +1139,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="C2:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
